--- a/Datos Experimentales/Data 24028.xlsx
+++ b/Datos Experimentales/Data 24028.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F6C440-D3AA-473D-A27E-09A149CC1E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1098,11 +1109,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1131,14 +1139,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1463,10 +1480,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1474,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1482,7 +1500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1490,7 +1508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1498,7 +1516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1514,7 +1532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1522,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1530,7 +1548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1538,7 +1556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1546,7 +1564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1554,7 +1572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1562,7 +1580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1570,7 +1588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1578,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1586,7 +1604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1594,7 +1612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1602,7 +1620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1610,7 +1628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1618,7 +1636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1626,7 +1644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1634,7 +1652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1650,7 +1668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1658,7 +1676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1666,7 +1684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1674,7 +1692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1682,7 +1700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1690,7 +1708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1698,7 +1716,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1706,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1714,7 +1732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1722,7 +1740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1730,7 +1748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1738,7 +1756,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1746,7 +1764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1754,7 +1772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1762,7 +1780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1770,7 +1788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1778,7 +1796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1786,7 +1804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1794,7 +1812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1802,7 +1820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1810,7 +1828,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1818,7 +1836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1826,7 +1844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1834,7 +1852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1842,7 +1860,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1850,7 +1868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1858,7 +1876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1866,7 +1884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1874,7 +1892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1882,7 +1900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1890,7 +1908,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1898,7 +1916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1906,7 +1924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1914,7 +1932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1922,7 +1940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1930,7 +1948,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1938,7 +1956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1946,7 +1964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1954,7 +1972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1962,7 +1980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1970,7 +1988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1978,7 +1996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1986,7 +2004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1994,7 +2012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -2002,7 +2020,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -2010,7 +2028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -2018,7 +2036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2026,7 +2044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2034,7 +2052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2042,7 +2060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2050,7 +2068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2058,7 +2076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2066,7 +2084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2074,7 +2092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2082,7 +2100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2090,7 +2108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2098,7 +2116,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2106,7 +2124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2114,7 +2132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2122,7 +2140,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2130,7 +2148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2138,7 +2156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2146,7 +2164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2154,7 +2172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2162,7 +2180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2170,7 +2188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2178,7 +2196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2186,7 +2204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2194,7 +2212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2202,7 +2220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2210,7 +2228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2218,7 +2236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2226,7 +2244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2234,7 +2252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2242,7 +2260,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2250,7 +2268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2258,7 +2276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2266,7 +2284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2274,7 +2292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2282,7 +2300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2290,7 +2308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2298,7 +2316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2306,7 +2324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2314,7 +2332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2322,7 +2340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2330,7 +2348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2338,7 +2356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2346,7 +2364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2354,7 +2372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2362,7 +2380,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2370,7 +2388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2378,7 +2396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2386,7 +2404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2394,7 +2412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2403,27 +2421,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B117"/>
+    <ignoredError sqref="A1:B117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2444,17 +2466,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -2465,7 +2489,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -2476,7 +2500,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -2487,29 +2511,29 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
       <c r="B4">
-        <v>0.7215277777777778</v>
+        <v>0.72152777777777777</v>
       </c>
       <c r="C4">
         <v>13.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
       <c r="B5">
-        <v>0.9715277777777778</v>
+        <v>0.97152777777777777</v>
       </c>
       <c r="C5">
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -2520,7 +2544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -2531,7 +2555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -2542,7 +2566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -2553,7 +2577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
@@ -2564,7 +2588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
@@ -2575,7 +2599,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
@@ -2586,7 +2610,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
@@ -2597,7 +2621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
@@ -2608,7 +2632,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
@@ -2619,7 +2643,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
@@ -2630,7 +2654,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
@@ -2641,271 +2665,271 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
       <c r="B18">
-        <v>4.221527777777778</v>
+        <v>4.2215277777777782</v>
       </c>
       <c r="C18">
         <v>13.6</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
       <c r="B19">
-        <v>4.471527777777778</v>
+        <v>4.4715277777777782</v>
       </c>
       <c r="C19">
         <v>13.6</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
       <c r="B20">
-        <v>4.721527777777778</v>
+        <v>4.7215277777777782</v>
       </c>
       <c r="C20">
         <v>13.5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
       <c r="B21">
-        <v>4.971527777777778</v>
+        <v>4.9715277777777782</v>
       </c>
       <c r="C21">
         <v>13.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
       <c r="B22">
-        <v>5.221527777777778</v>
+        <v>5.2215277777777782</v>
       </c>
       <c r="C22">
         <v>13.6</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
       <c r="B23">
-        <v>5.471527777777778</v>
+        <v>5.4715277777777782</v>
       </c>
       <c r="C23">
         <v>13.7</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
       <c r="B24">
-        <v>5.721527777777778</v>
+        <v>5.7215277777777782</v>
       </c>
       <c r="C24">
         <v>14</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
       <c r="B25">
-        <v>5.971527777777778</v>
+        <v>5.9715277777777782</v>
       </c>
       <c r="C25">
         <v>14</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
       <c r="B26">
-        <v>6.221527777777778</v>
+        <v>6.2215277777777782</v>
       </c>
       <c r="C26">
         <v>13.6</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
       <c r="B27">
-        <v>6.471527777777778</v>
+        <v>6.4715277777777782</v>
       </c>
       <c r="C27">
         <v>13.6</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
       <c r="B28">
-        <v>6.721527777777778</v>
+        <v>6.7215277777777782</v>
       </c>
       <c r="C28">
         <v>13.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
       <c r="B29">
-        <v>6.971527777777778</v>
+        <v>6.9715277777777782</v>
       </c>
       <c r="C29">
         <v>14</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
       <c r="B30">
-        <v>7.221527777777778</v>
+        <v>7.2215277777777782</v>
       </c>
       <c r="C30">
         <v>14.2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
       <c r="B31">
-        <v>7.471527777777778</v>
+        <v>7.4715277777777782</v>
       </c>
       <c r="C31">
         <v>13.4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
       <c r="B32">
-        <v>7.721527777777778</v>
+        <v>7.7215277777777782</v>
       </c>
       <c r="C32">
         <v>14.7</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
       <c r="B33">
-        <v>7.971527777777778</v>
+        <v>7.9715277777777782</v>
       </c>
       <c r="C33">
         <v>14.1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
       <c r="B34">
-        <v>8.221527777777778</v>
+        <v>8.2215277777777782</v>
       </c>
       <c r="C34">
         <v>13.8</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
       <c r="B35">
-        <v>8.471527777777778</v>
+        <v>8.4715277777777782</v>
       </c>
       <c r="C35">
         <v>14.2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
       <c r="B36">
-        <v>8.721527777777778</v>
+        <v>8.7215277777777782</v>
       </c>
       <c r="C36">
         <v>14.6</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
       <c r="B37">
-        <v>8.971527777777778</v>
+        <v>8.9715277777777782</v>
       </c>
       <c r="C37">
         <v>13.4</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
       <c r="B38">
-        <v>9.221527777777778</v>
+        <v>9.2215277777777782</v>
       </c>
       <c r="C38">
         <v>13.9</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
       <c r="B39">
-        <v>9.471527777777778</v>
+        <v>9.4715277777777782</v>
       </c>
       <c r="C39">
         <v>13.6</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
       <c r="B40">
-        <v>9.721527777777778</v>
+        <v>9.7215277777777782</v>
       </c>
       <c r="C40">
         <v>14.5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
       <c r="B41">
-        <v>9.971527777777778</v>
+        <v>9.9715277777777782</v>
       </c>
       <c r="C41">
         <v>14.7</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
@@ -2916,7 +2940,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
@@ -2927,7 +2951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
@@ -2938,7 +2962,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
@@ -2949,7 +2973,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>325</v>
       </c>
@@ -2960,7 +2984,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>326</v>
       </c>
@@ -2971,7 +2995,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>327</v>
       </c>
@@ -2982,7 +3006,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2993,7 +3017,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>329</v>
       </c>
@@ -3004,7 +3028,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>330</v>
       </c>
@@ -3015,7 +3039,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>331</v>
       </c>
@@ -3026,7 +3050,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>332</v>
       </c>
@@ -3037,7 +3061,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>333</v>
       </c>
@@ -3048,7 +3072,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>334</v>
       </c>
@@ -3059,7 +3083,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>335</v>
       </c>
@@ -3070,7 +3094,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>336</v>
       </c>
@@ -3081,7 +3105,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>337</v>
       </c>
@@ -3092,7 +3116,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>338</v>
       </c>
@@ -3103,7 +3127,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>339</v>
       </c>
@@ -3114,7 +3138,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>340</v>
       </c>
@@ -3125,7 +3149,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>341</v>
       </c>
@@ -3136,7 +3160,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>342</v>
       </c>
@@ -3147,7 +3171,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>343</v>
       </c>
@@ -3158,7 +3182,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>344</v>
       </c>
@@ -3169,7 +3193,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>345</v>
       </c>
@@ -3180,7 +3204,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
@@ -3191,7 +3215,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
@@ -3202,7 +3226,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
@@ -3213,7 +3237,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
@@ -3224,7 +3248,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -3235,7 +3259,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -3246,7 +3270,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -3257,7 +3281,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
@@ -3269,17 +3293,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C74"/>
+    <ignoredError sqref="A1:C74" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -3290,7 +3316,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -3301,7 +3327,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -3312,29 +3338,29 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
       <c r="B4">
-        <v>0.7215277777777778</v>
+        <v>0.72152777777777777</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
       <c r="B5">
-        <v>0.9715277777777778</v>
+        <v>0.97152777777777777</v>
       </c>
       <c r="C5">
         <v>1085</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -3345,7 +3371,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -3356,7 +3382,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -3367,7 +3393,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -3378,7 +3404,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
@@ -3389,7 +3415,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
@@ -3400,7 +3426,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
@@ -3411,7 +3437,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
@@ -3422,7 +3448,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
@@ -3433,7 +3459,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
@@ -3444,7 +3470,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
@@ -3455,7 +3481,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
@@ -3466,271 +3492,271 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
       <c r="B18">
-        <v>4.221527777777778</v>
+        <v>4.2215277777777782</v>
       </c>
       <c r="C18">
         <v>1050</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
       <c r="B19">
-        <v>4.471527777777778</v>
+        <v>4.4715277777777782</v>
       </c>
       <c r="C19">
         <v>1045</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
       <c r="B20">
-        <v>4.721527777777778</v>
+        <v>4.7215277777777782</v>
       </c>
       <c r="C20">
         <v>1041</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
       <c r="B21">
-        <v>4.971527777777778</v>
+        <v>4.9715277777777782</v>
       </c>
       <c r="C21">
         <v>1040</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
       <c r="B22">
-        <v>5.221527777777778</v>
+        <v>5.2215277777777782</v>
       </c>
       <c r="C22">
         <v>1037</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
       <c r="B23">
-        <v>5.471527777777778</v>
+        <v>5.4715277777777782</v>
       </c>
       <c r="C23">
         <v>1033</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
       <c r="B24">
-        <v>5.721527777777778</v>
+        <v>5.7215277777777782</v>
       </c>
       <c r="C24">
         <v>1028</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
       <c r="B25">
-        <v>5.971527777777778</v>
+        <v>5.9715277777777782</v>
       </c>
       <c r="C25">
         <v>1027</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
       <c r="B26">
-        <v>6.221527777777778</v>
+        <v>6.2215277777777782</v>
       </c>
       <c r="C26">
         <v>1026</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
       <c r="B27">
-        <v>6.471527777777778</v>
+        <v>6.4715277777777782</v>
       </c>
       <c r="C27">
         <v>1023</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
       <c r="B28">
-        <v>6.721527777777778</v>
+        <v>6.7215277777777782</v>
       </c>
       <c r="C28">
         <v>1021</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
       <c r="B29">
-        <v>6.971527777777778</v>
+        <v>6.9715277777777782</v>
       </c>
       <c r="C29">
         <v>1020</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
       <c r="B30">
-        <v>7.221527777777778</v>
+        <v>7.2215277777777782</v>
       </c>
       <c r="C30">
         <v>1019</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
       <c r="B31">
-        <v>7.471527777777778</v>
+        <v>7.4715277777777782</v>
       </c>
       <c r="C31">
         <v>1018</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
       <c r="B32">
-        <v>7.721527777777778</v>
+        <v>7.7215277777777782</v>
       </c>
       <c r="C32">
         <v>1015</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
       <c r="B33">
-        <v>7.971527777777778</v>
+        <v>7.9715277777777782</v>
       </c>
       <c r="C33">
         <v>1014</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
       <c r="B34">
-        <v>8.221527777777778</v>
+        <v>8.2215277777777782</v>
       </c>
       <c r="C34">
         <v>1013</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
       <c r="B35">
-        <v>8.471527777777778</v>
+        <v>8.4715277777777782</v>
       </c>
       <c r="C35">
         <v>1011</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
       <c r="B36">
-        <v>8.721527777777778</v>
+        <v>8.7215277777777782</v>
       </c>
       <c r="C36">
         <v>1011</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
       <c r="B37">
-        <v>8.971527777777778</v>
+        <v>8.9715277777777782</v>
       </c>
       <c r="C37">
         <v>1010</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
       <c r="B38">
-        <v>9.221527777777778</v>
+        <v>9.2215277777777782</v>
       </c>
       <c r="C38">
         <v>1009</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
       <c r="B39">
-        <v>9.471527777777778</v>
+        <v>9.4715277777777782</v>
       </c>
       <c r="C39">
         <v>1008</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
       <c r="B40">
-        <v>9.721527777777778</v>
+        <v>9.7215277777777782</v>
       </c>
       <c r="C40">
         <v>1006</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
       <c r="B41">
-        <v>9.971527777777778</v>
+        <v>9.9715277777777782</v>
       </c>
       <c r="C41">
         <v>1005</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
@@ -3741,7 +3767,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
@@ -3752,7 +3778,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
@@ -3763,7 +3789,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
@@ -3774,7 +3800,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>325</v>
       </c>
@@ -3785,7 +3811,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>326</v>
       </c>
@@ -3796,7 +3822,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>327</v>
       </c>
@@ -3807,7 +3833,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -3818,7 +3844,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>329</v>
       </c>
@@ -3829,7 +3855,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>330</v>
       </c>
@@ -3840,7 +3866,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>331</v>
       </c>
@@ -3851,7 +3877,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>332</v>
       </c>
@@ -3862,7 +3888,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>333</v>
       </c>
@@ -3873,7 +3899,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>334</v>
       </c>
@@ -3884,7 +3910,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>335</v>
       </c>
@@ -3895,7 +3921,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>336</v>
       </c>
@@ -3906,7 +3932,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>337</v>
       </c>
@@ -3917,7 +3943,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>338</v>
       </c>
@@ -3928,7 +3954,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>339</v>
       </c>
@@ -3939,7 +3965,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>340</v>
       </c>
@@ -3950,7 +3976,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>341</v>
       </c>
@@ -3961,7 +3987,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>342</v>
       </c>
@@ -3972,7 +3998,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>343</v>
       </c>
@@ -3983,7 +4009,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>344</v>
       </c>
@@ -3994,7 +4020,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>345</v>
       </c>
@@ -4005,7 +4031,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
@@ -4016,7 +4042,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
@@ -4027,7 +4053,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
@@ -4038,7 +4064,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
@@ -4049,7 +4075,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -4060,7 +4086,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -4071,7 +4097,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -4082,7 +4108,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
@@ -4094,17 +4120,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C74"/>
+    <ignoredError sqref="A1:C74" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -4128,17 +4156,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4452,7 +4482,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -4580,7 +4610,7 @@
         <v>13.8</v>
       </c>
       <c r="AT2">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -4676,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="BZ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -4718,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="CN2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -4746,17 +4776,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CZ2"/>
+    <ignoredError sqref="A1:CZ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -4809,7 +4841,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -4838,7 +4870,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9847</v>
       </c>
@@ -4873,7 +4905,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9847</v>
       </c>
@@ -4902,7 +4934,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9847</v>
       </c>
@@ -4916,7 +4948,7 @@
         <v>188</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>184</v>
@@ -4952,7 +4984,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9847</v>
       </c>
@@ -4966,7 +4998,7 @@
         <v>188</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>184</v>
@@ -5002,7 +5034,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9847</v>
       </c>
@@ -5037,7 +5069,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9847</v>
       </c>
@@ -5084,7 +5116,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9847</v>
       </c>
@@ -5113,7 +5145,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9847</v>
       </c>
@@ -5148,7 +5180,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9847</v>
       </c>
@@ -5183,7 +5215,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9847</v>
       </c>
@@ -5219,17 +5251,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -5261,7 +5295,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -5293,7 +5327,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9847</v>
       </c>
@@ -5325,7 +5359,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9847</v>
       </c>
@@ -5358,27 +5392,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -5410,7 +5448,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -5443,17 +5481,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -5470,7 +5510,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -5482,27 +5522,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>163</v>
       </c>
@@ -5552,7 +5596,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9847</v>
       </c>
@@ -5565,7 +5609,7 @@
       <c r="D2">
         <v>6822</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F2" t="s">
@@ -5596,13 +5640,13 @@
         <v>246</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9847</v>
       </c>
@@ -5615,7 +5659,7 @@
       <c r="D3">
         <v>6822</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F3" t="s">
@@ -5646,13 +5690,13 @@
         <v>246</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9847</v>
       </c>
@@ -5665,7 +5709,7 @@
       <c r="D4">
         <v>6822</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F4" t="s">
@@ -5702,7 +5746,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9847</v>
       </c>
@@ -5715,7 +5759,7 @@
       <c r="D5">
         <v>6822</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F5" t="s">
@@ -5752,7 +5796,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9847</v>
       </c>
@@ -5765,7 +5809,7 @@
       <c r="D6">
         <v>6822</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F6" t="s">
@@ -5802,7 +5846,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9847</v>
       </c>
@@ -5815,7 +5859,7 @@
       <c r="D7">
         <v>6822</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F7" t="s">
@@ -5852,7 +5896,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9847</v>
       </c>
@@ -5865,7 +5909,7 @@
       <c r="D8">
         <v>6822</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.779456018514</v>
       </c>
       <c r="F8" t="s">
@@ -5902,7 +5946,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9847</v>
       </c>
@@ -5915,8 +5959,8 @@
       <c r="D9">
         <v>6889</v>
       </c>
-      <c r="E9">
-        <v>45376.65908564815</v>
+      <c r="E9" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F9" t="s">
         <v>134</v>
@@ -5946,13 +5990,13 @@
         <v>246</v>
       </c>
       <c r="O9">
-        <v>7.7571</v>
+        <v>7.7571000000000003</v>
       </c>
       <c r="P9" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9847</v>
       </c>
@@ -5965,8 +6009,8 @@
       <c r="D10">
         <v>6889</v>
       </c>
-      <c r="E10">
-        <v>45376.65908564815</v>
+      <c r="E10" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -6002,7 +6046,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9847</v>
       </c>
@@ -6015,8 +6059,8 @@
       <c r="D11">
         <v>6889</v>
       </c>
-      <c r="E11">
-        <v>45376.65908564815</v>
+      <c r="E11" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
@@ -6052,7 +6096,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9847</v>
       </c>
@@ -6065,8 +6109,8 @@
       <c r="D12">
         <v>6889</v>
       </c>
-      <c r="E12">
-        <v>45376.65908564815</v>
+      <c r="E12" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
@@ -6102,7 +6146,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9847</v>
       </c>
@@ -6115,8 +6159,8 @@
       <c r="D13">
         <v>6889</v>
       </c>
-      <c r="E13">
-        <v>45376.65908564815</v>
+      <c r="E13" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F13" t="s">
         <v>134</v>
@@ -6152,7 +6196,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9847</v>
       </c>
@@ -6165,8 +6209,8 @@
       <c r="D14">
         <v>6889</v>
       </c>
-      <c r="E14">
-        <v>45376.65908564815</v>
+      <c r="E14" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F14" t="s">
         <v>134</v>
@@ -6196,13 +6240,13 @@
         <v>246</v>
       </c>
       <c r="O14">
-        <v>38.7</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="P14" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9847</v>
       </c>
@@ -6215,8 +6259,8 @@
       <c r="D15">
         <v>6889</v>
       </c>
-      <c r="E15">
-        <v>45376.65908564815</v>
+      <c r="E15" s="1">
+        <v>45373.659085648149</v>
       </c>
       <c r="F15" t="s">
         <v>134</v>
@@ -6252,7 +6296,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9847</v>
       </c>
@@ -6265,8 +6309,8 @@
       <c r="D16">
         <v>7319</v>
       </c>
-      <c r="E16">
-        <v>45389.67936342592</v>
+      <c r="E16" s="1">
+        <v>45389.679363425923</v>
       </c>
       <c r="F16" t="s">
         <v>134</v>
@@ -6302,7 +6346,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9847</v>
       </c>
@@ -6315,7 +6359,7 @@
       <c r="D17">
         <v>7412</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>45391.681134259255</v>
       </c>
       <c r="F17" t="s">
@@ -6352,7 +6396,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9847</v>
       </c>
@@ -6365,8 +6409,8 @@
       <c r="D18">
         <v>7441</v>
       </c>
-      <c r="E18">
-        <v>45392.58760416666</v>
+      <c r="E18" s="1">
+        <v>45392.587604166663</v>
       </c>
       <c r="F18" t="s">
         <v>134</v>
@@ -6402,7 +6446,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9847</v>
       </c>
@@ -6415,7 +6459,7 @@
       <c r="D19">
         <v>7464</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F19" t="s">
@@ -6452,7 +6496,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9847</v>
       </c>
@@ -6465,7 +6509,7 @@
       <c r="D20">
         <v>7464</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F20" t="s">
@@ -6496,13 +6540,13 @@
         <v>246</v>
       </c>
       <c r="O20">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P20" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9847</v>
       </c>
@@ -6515,7 +6559,7 @@
       <c r="D21">
         <v>7464</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F21" t="s">
@@ -6552,7 +6596,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9847</v>
       </c>
@@ -6565,7 +6609,7 @@
       <c r="D22">
         <v>7464</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F22" t="s">
@@ -6602,7 +6646,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9847</v>
       </c>
@@ -6615,7 +6659,7 @@
       <c r="D23">
         <v>7464</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F23" t="s">
@@ -6652,7 +6696,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9847</v>
       </c>
@@ -6665,7 +6709,7 @@
       <c r="D24">
         <v>7464</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F24" t="s">
@@ -6702,7 +6746,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9847</v>
       </c>
@@ -6715,7 +6759,7 @@
       <c r="D25">
         <v>7464</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F25" t="s">
@@ -6752,7 +6796,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9847</v>
       </c>
@@ -6765,7 +6809,7 @@
       <c r="D26">
         <v>7464</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F26" t="s">
@@ -6802,7 +6846,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9847</v>
       </c>
@@ -6815,7 +6859,7 @@
       <c r="D27">
         <v>7464</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F27" t="s">
@@ -6852,7 +6896,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9847</v>
       </c>
@@ -6865,7 +6909,7 @@
       <c r="D28">
         <v>7464</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>45392.842939814815</v>
       </c>
       <c r="F28" t="s">
@@ -6902,7 +6946,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9847</v>
       </c>
@@ -6915,8 +6959,8 @@
       <c r="D29">
         <v>7584</v>
       </c>
-      <c r="E29">
-        <v>45396.91048611111</v>
+      <c r="E29" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F29" t="s">
         <v>134</v>
@@ -6952,7 +6996,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9847</v>
       </c>
@@ -6965,8 +7009,8 @@
       <c r="D30">
         <v>7584</v>
       </c>
-      <c r="E30">
-        <v>45396.91048611111</v>
+      <c r="E30" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F30" t="s">
         <v>134</v>
@@ -6996,13 +7040,13 @@
         <v>246</v>
       </c>
       <c r="O30">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P30" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9847</v>
       </c>
@@ -7015,8 +7059,8 @@
       <c r="D31">
         <v>7584</v>
       </c>
-      <c r="E31">
-        <v>45396.91048611111</v>
+      <c r="E31" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F31" t="s">
         <v>134</v>
@@ -7052,7 +7096,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9847</v>
       </c>
@@ -7065,8 +7109,8 @@
       <c r="D32">
         <v>7584</v>
       </c>
-      <c r="E32">
-        <v>45396.91048611111</v>
+      <c r="E32" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F32" t="s">
         <v>134</v>
@@ -7102,7 +7146,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9847</v>
       </c>
@@ -7115,8 +7159,8 @@
       <c r="D33">
         <v>7584</v>
       </c>
-      <c r="E33">
-        <v>45396.91048611111</v>
+      <c r="E33" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F33" t="s">
         <v>134</v>
@@ -7152,7 +7196,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9847</v>
       </c>
@@ -7165,8 +7209,8 @@
       <c r="D34">
         <v>7584</v>
       </c>
-      <c r="E34">
-        <v>45396.91048611111</v>
+      <c r="E34" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F34" t="s">
         <v>134</v>
@@ -7202,7 +7246,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9847</v>
       </c>
@@ -7215,8 +7259,8 @@
       <c r="D35">
         <v>7584</v>
       </c>
-      <c r="E35">
-        <v>45396.91048611111</v>
+      <c r="E35" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F35" t="s">
         <v>134</v>
@@ -7252,7 +7296,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9847</v>
       </c>
@@ -7265,8 +7309,8 @@
       <c r="D36">
         <v>7584</v>
       </c>
-      <c r="E36">
-        <v>45396.91048611111</v>
+      <c r="E36" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F36" t="s">
         <v>134</v>
@@ -7302,7 +7346,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9847</v>
       </c>
@@ -7315,8 +7359,8 @@
       <c r="D37">
         <v>7584</v>
       </c>
-      <c r="E37">
-        <v>45396.91048611111</v>
+      <c r="E37" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F37" t="s">
         <v>134</v>
@@ -7352,7 +7396,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9847</v>
       </c>
@@ -7365,8 +7409,8 @@
       <c r="D38">
         <v>7584</v>
       </c>
-      <c r="E38">
-        <v>45396.91048611111</v>
+      <c r="E38" s="1">
+        <v>45396.910486111112</v>
       </c>
       <c r="F38" t="s">
         <v>134</v>
@@ -7403,8 +7447,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P38"/>
+    <ignoredError sqref="A1:P8 A16:P38 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>